--- a/SGC-CKN/Excel/5bd0efe9-e534-4099-9568-36afa66b8266_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-1_D800_11-03-2026.xlsx
+++ b/SGC-CKN/Excel/5bd0efe9-e534-4099-9568-36afa66b8266_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-1_D800_11-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>17-1</t>
+    <t>17-01</t>
   </si>
   <si>
     <t>Biên bản số</t>
